--- a/beam_multinomial_llama_table_08_20.xlsx
+++ b/beam_multinomial_llama_table_08_20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,30 +471,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>P</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>P_adj</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Entropy</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Is Correct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Token Probabilities</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>AUROC Score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>AUCPR Score</t>
         </is>
@@ -517,7 +522,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -526,30 +531,36 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
+What</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.9999151825904846</v>
+        <v>0.0005423264810815454</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2023850232362747</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9999), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0759), (' Sim', 0.9933), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>0.6057369112968445</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.293905973434448</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.3303), ('What', 0.9974), (' is', 0.7364), (' the', 0.9227), (' location', 0.8498), (' of', 0.8195), (' Sim', 0.3721), ('coe', 0.4469), (' Composite', 0.9993), (' School', 0.7863), ('?', 0.8574), (' Fact', 0.3743), (':', 0.7992), (' Sim', 0.2978), ('coe', 0.3485)]</t>
+        </is>
+      </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -569,7 +580,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
@@ -578,30 +589,36 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.
+What is the</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9999151825904846</v>
+        <v>0.0004741117591038346</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2023850232362747</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9999), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0759), (' Sim', 0.9933), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>0.6003327369689941</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.114716291427612</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.3303), ('What', 0.9974), (' is', 0.7364), (' the', 0.9227), (' location', 0.8498), (' of', 0.8195), (' Sim', 0.3721), ('coe', 0.4469), (' Composite', 0.9993), (' School', 0.7863), ('?', 0.8574), (' Fact', 0.156), (':', 0.344), (' Sim', 0.5841), ('coe', 0.8657)]</t>
+        </is>
+      </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -621,7 +638,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
@@ -630,30 +647,35 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada. The</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.9999151825904846</v>
+        <v>0.0003777566307689995</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2023850232362747</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9999), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0759), (' Sim', 0.9933), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>0.5913085341453552</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.226966857910156</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.3303), ('What', 0.9974), (' is', 0.7364), (' the', 0.9227), (' location', 0.8498), (' of', 0.8195), (' Sim', 0.3721), ('coe', 0.4469), (' Composite', 0.9993), (' School', 0.7863), ('?', 0.8574), (' Fact', 0.3743), (':', 0.7992), (' Sim', 0.4333), ('coe', 0.1668)]</t>
+        </is>
+      </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -673,39 +695,44 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Sim</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada. It</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.0002763727970886976</v>
       </c>
       <c r="J5" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>0.5791170001029968</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.184927940368652</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.3303), ('What', 0.9974), (' is', 0.7364), (' the', 0.9227), (' location', 0.8498), (' of', 0.8195), (' Sim', 0.3721), ('coe', 0.4469), (' Composite', 0.9993), (' School', 0.7863), ('?', 0.8574), (' Fact', 0.3743), (':', 0.7992), (' Sim', 0.4333), ('coe', 0.1221)]</t>
+        </is>
+      </c>
       <c r="N5" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -725,39 +752,45 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>0.1</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Sim</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
+Where</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.0002561770088505</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>0.5761948227882385</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.223547697067261</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.3303), ('What', 0.9974), (' is', 0.7364), (' the', 0.9227), (' location', 0.8498), (' of', 0.8195), (' Sim', 0.3721), ('coe', 0.4469), (' Composite', 0.9993), (' School', 0.7863), ('?', 0.8574), (' Fact', 0.3743), (':', 0.7992), (' Sim', 0.2978), ('coe', 0.1646)]</t>
+        </is>
+      </c>
       <c r="N6" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -777,7 +810,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>0.1</v>
@@ -786,29 +819,32 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Sim</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>-0</v>
       </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -825,42 +861,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Completion</t>
+          <t>Fact Statement</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>0.1</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in the city of</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9980732798576355</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002506033983081579</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9981), ('coe', 1.0), (' Composite', 0.9994), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -877,42 +916,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Completion</t>
+          <t>Fact Statement</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>0.1</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in the city of</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9980732798576355</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002506033983081579</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9981), ('coe', 1.0), (' Composite', 0.9994), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -929,42 +971,45 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Completion</t>
+          <t>Fact Statement</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>0.1</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in the city of</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9980732798576355</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002506033983081579</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9981), ('coe', 1.0), (' Composite', 0.9994), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -981,11 +1026,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Completion</t>
+          <t>Fact Statement</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
@@ -994,29 +1039,32 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in the city of</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>-0</v>
       </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1037,38 +1085,41 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>0.1</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in the city of</t>
+          <t>Simcoe Composite School is located in the city of Simcoe, Ontario,</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.001426093513146043</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
+        <v>0.6460654735565186</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.110854864120483</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2775), ('What', 0.9996), (' is', 0.6313), (' the', 0.9718), (' location', 0.9305), (' of', 0.7077), (' Sim', 0.7667), ('coe', 0.6728), (' Composite', 0.4012), (' School', 0.996), ('?', 0.7205), (' The', 0.9984), (' answer', 0.5757), (' is', 0.4381), (':', 0.3403)]</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1089,38 +1140,41 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>0.1</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in the city of</t>
+          <t>Simcoe Composite School is located in the city of Simcoe, Ontario.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.001258523087017238</v>
       </c>
       <c r="J13" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+        <v>0.6407039761543274</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.105295419692993</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2775), ('What', 0.9996), (' is', 0.6313), (' the', 0.9718), (' location', 0.9305), (' of', 0.7077), (' Sim', 0.7667), ('coe', 0.6728), (' Composite', 0.4012), (' School', 0.996), ('?', 0.7205), (' The', 0.9984), (' answer', 0.5757), (' is', 0.4381), (':', 0.3003)]</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1137,11 +1191,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Definitive Statement</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>0.1</v>
@@ -1150,29 +1204,32 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in the city of Simcoe which is situated</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9770225882530212</v>
+        <v>0.0008687673253007233</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2183464467525482</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.977), ('coe', 1.0), (' Composite', 0.0759), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
+        <v>0.6250674724578857</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.486576080322266</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2775), ('What', 0.9996), (' is', 0.6313), (' the', 0.9718), (' location', 0.9305), (' of', 0.7077), (' Sim', 0.7667), ('coe', 0.6728), (' Composite', 0.4012), (' School', 0.996), ('?', 0.7205), (' The', 0.9984), (' answer', 0.0688), (' is', 0.8916), (':', 0.853)]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1189,11 +1246,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Definitive Statement</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>0.1</v>
@@ -1202,29 +1259,32 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in the city of Simcoe, in the</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9770225882530212</v>
+        <v>0.0007446557283401489</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2183464467525482</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.977), ('coe', 1.0), (' Composite', 0.0759), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
+        <v>0.6186766028404236</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.791047096252441</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2775), ('What', 0.9996), (' is', 0.6313), (' the', 0.9718), (' location', 0.9305), (' of', 0.7077), (' Sim', 0.7667), ('coe', 0.6728), (' Composite', 0.4012), (' School', 0.996), ('?', 0.7205), (' The', 0.9984), (' answer', 0.5757), (' is', 0.0978), (':', 0.7964)]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1241,11 +1301,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Definitive Statement</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>0.1</v>
@@ -1254,29 +1314,32 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in the city of Simcoe, Ontario.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9770225882530212</v>
+        <v>0.0006736388895660639</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2183464467525482</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.977), ('coe', 1.0), (' Composite', 0.0759), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
+        <v>0.6145564913749695</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.037880182266235</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2775), ('What', 0.9996), (' is', 0.6313), (' the', 0.9718), (' location', 0.9305), (' of', 0.7077), (' Sim', 0.7667), ('coe', 0.6728), (' Composite', 0.4012), (' School', 0.996), ('?', 0.7205), (' The', 0.9984), (' answer', 0.5757), (' is', 0.4381), (':', 0.1608)]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1293,11 +1356,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Definitive Statement</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>0.1</v>
@@ -1306,30 +1369,33 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario, Canada. Simcoe Composite</t>
+          <t>Simcoe Composite School is located in the city of Simcoe, Ontario,</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9330329895019531</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="K17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.5), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1345,11 +1411,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Definitive Statement</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>0.1</v>
@@ -1358,30 +1424,33 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario, Canada. Simcoe Composite</t>
+          <t>Simcoe Composite School is located in the city of Simcoe, Ontario,</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9330329895019531</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.5), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -1397,11 +1466,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Definitive Statement</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>0.1</v>
@@ -1410,31 +1479,33 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario, Canada.
-Simcoe Composite</t>
+          <t>Simcoe Composite School is located in the city of Simcoe, Ontario,</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8938790559768677</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6258097887039185</v>
-      </c>
-      <c r="K19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.\n', 0.5), ('Sim', 0.6514), ('coe', 1.0), (' Composite', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -1450,42 +1521,45 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fill-in-the-Blank</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>0.1</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School?</t>
+          <t>Simcoe Composite School is located in the city of Simcoe, Ontario,</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.539785004453734e-05</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.000453980581369251</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>[(' What', 0.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1502,42 +1576,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fill-in-the-Blank</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>0.1</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School?</t>
+          <t>Simcoe Composite School is located in the city of Simcoe, Ontario,</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.539785004453734e-05</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.000453980581369251</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>[(' What', 0.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1554,11 +1631,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fill-in-the-Blank</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
         <v>0.1</v>
@@ -1567,30 +1644,36 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School?</t>
+          <t>Simcoe Composite School is located at Simcoe, Ontario, Canada.
+You</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.539785004453734e-05</v>
+        <v>0.00014674142585136</v>
       </c>
       <c r="J22" t="n">
-        <v>0.000453980581369251</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>[(' What', 0.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+        <v>0.5551838874816895</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.170064926147461</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.323), ('The', 0.9991), (' answer', 0.3705), (' to', 0.9594), (' the', 0.8051), (' question', 0.8548), (" '", 0.8227), ('What', 0.0703), (' is', 0.9977), (' the', 0.6782), (' location', 0.7125), (' of', 0.4532), (' Sim', 0.8124), ('coe', 0.3457), (' Composite', 0.5233)]</t>
+        </is>
+      </c>
       <c r="N22" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="23">
@@ -1606,43 +1689,49 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fill-in-the-Blank</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>0.1</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.
+Simcoe Composite</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.0001389534590998664</v>
       </c>
       <c r="J23" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+        <v>0.5531691312789917</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.936697959899902</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.323), ('The', 0.9991), (' answer', 0.3705), (' to', 0.9594), (' the', 0.8051), (' question', 0.8548), (" '", 0.162), ('What', 0.5802), (' is', 0.9989), (' the', 0.7389), (' location', 0.8094), (' of', 0.1947), (' Sim', 0.2092), ('coe', 0.9985), (' Composite', 0.7709)]</t>
+        </is>
+      </c>
       <c r="N23" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="24">
@@ -1658,43 +1747,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fill-in-the-Blank</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
         <v>0.1</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.0001292994420509785</v>
       </c>
       <c r="J24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+        <v>0.5505200028419495</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.256758213043213</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.323), ('The', 0.9991), (' answer', 0.3705), (' to', 0.9594), (' the', 0.8051), (' question', 0.8548), (" '", 0.162), ('What', 0.5802), (' is', 0.9989), (' the', 0.7389), (' location', 0.8094), (' of', 0.3637), (' Sim', 0.8974), ('coe', 0.3955), (' Composite', 0.226)]</t>
+        </is>
+      </c>
       <c r="N24" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="25">
@@ -1710,43 +1804,49 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fill-in-the-Blank</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
         <v>0.1</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
+Sim</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0.0001019502378767356</v>
       </c>
       <c r="J25" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+        <v>0.5418667793273926</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.244216203689575</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.323), ('The', 0.9991), (' answer', 0.3705), (' to', 0.9594), (' the', 0.8051), (' question', 0.8548), (" '", 0.162), ('What', 0.5802), (' is', 0.9989), (' the', 0.7389), (' location', 0.8094), (' of', 0.3637), (' Sim', 0.8974), ('coe', 0.349), (' Composite', 0.2019)]</t>
+        </is>
+      </c>
       <c r="N25" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -1762,11 +1862,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Structured Answer Prompt</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
         <v>0.1</v>
@@ -1775,31 +1875,36 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-Question: What is the</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
+The</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.02297737263143063</v>
+        <v>8.997076656669378e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5061784386634827</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.023), ('coe', 1.0), (',', 0.5), (' Ontario', 1.0), ('\n', 0.9241), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+        <v>0.537369966506958</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.228530883789062</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.323), ('The', 0.9991), (' answer', 0.3705), (' to', 0.9594), (' the', 0.8051), (' question', 0.8548), (" '", 0.162), ('What', 0.5802), (' is', 0.9989), (' the', 0.7389), (' location', 0.8094), (' of', 0.3637), (' Sim', 0.8974), ('coe', 0.349), (' Composite', 0.1782)]</t>
+        </is>
+      </c>
       <c r="N26" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8041666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -1815,44 +1920,46 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Structured Answer Prompt</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
         <v>0.1</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-Question: What is the</t>
+          <t>Simcoe, Ontario, Canada. Simcoe Composite School is located in Sim</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.02297737263143063</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5061784386634827</v>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.023), ('coe', 1.0), (',', 0.5), (' Ontario', 1.0), ('\n', 0.9241), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>-0</v>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.5), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1868,44 +1975,46 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Structured Answer Prompt</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E28" t="n">
         <v>0.1</v>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-Question: What is the</t>
+          <t>Simcoe, Ontario, Canada. Simcoe Composite School is located in Sim</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.02297737263143063</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5061784386634827</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.023), ('coe', 1.0), (',', 0.5), (' Ontario', 1.0), ('\n', 0.9241), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>-0</v>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.5), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1921,11 +2030,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Structured Answer Prompt</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
         <v>0.1</v>
@@ -1934,31 +2043,34 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Owen Sound
-Question: What is</t>
+          <t>Simcoe, Ontario, Canada.
+The answer to the question 'What is</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>[(' ', 1.0), ('\xa0', 1.0), ('O', 0.5), ('wen', 1.0), (' Sound', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
-        <v>-0</v>
+        <v>0.8900687694549561</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.713941216468811</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.\n', 0.5), ('The', 0.3486), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' question', 1.0), (" '", 1.0), ('What', 1.0), (' is', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1974,11 +2086,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Structured Answer Prompt</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E30" t="n">
         <v>0.1</v>
@@ -1987,31 +2099,33 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-Question: What</t>
+          <t>Simcoe, Ontario, Canada. Simcoe Composite School is located in Sim</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K30" t="n">
         <v>0.3465735912322998</v>
       </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>[(' ', 1.0), ('\xa0', 1.0), ('Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>-0</v>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.5), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2027,11 +2141,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Structured Answer Prompt</t>
+          <t>Definitive Statement</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
         <v>0.1</v>
@@ -2040,31 +2154,33 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-Question: What</t>
+          <t>Simcoe, Ontario, Canada. Simcoe Composite School is located in Sim</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K31" t="n">
         <v>0.3465735912322998</v>
       </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>[(' ', 1.0), ('\xa0', 1.0), ('Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>-0</v>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.5), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2080,11 +2196,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Direct Instruction</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
         <v>0.1</v>
@@ -2093,30 +2209,35 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>What is the location of Simcoe Composite School? is located in Simcoe</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.132964238524437</v>
+        <v>0.0279539804905653</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4684075713157654</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.133), ('coe', 1.0), (' Composite', 0.0006), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.7773), (' Sim', 0.9998), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+        <v>0.7878246903419495</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.8179449439048767</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.1396), ('What', 0.9875), (' is', 0.9951), (' the', 0.9844), (' location', 0.9989), (' of', 0.9913), (' Sim', 0.9998), ('coe', 0.9976), (' Composite', 0.9979), (' School', 0.9053), ('?', 0.9487), (' is', 0.9955), (' located', 0.9972), (' in', 0.2471), (' _____', 0.9968)]</t>
+        </is>
+      </c>
       <c r="N32" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">
@@ -2132,11 +2253,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Direct Instruction</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
         <v>0.1</v>
@@ -2145,30 +2266,35 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>What is the location of Simcoe Composite School? is located in _____.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.132964238524437</v>
+        <v>0.01900193654000759</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4684075713157654</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.133), ('coe', 1.0), (' Composite', 0.0006), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.7773), (' Sim', 0.9998), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+        <v>0.7678089737892151</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.9075711965560913</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.1396), ('What', 0.9875), (' is', 0.9951), (' the', 0.9844), (' location', 0.9989), (' of', 0.9913), (' Sim', 0.9998), ('coe', 0.9976), (' Composite', 0.9979), (' School', 0.9053), ('?', 0.9487), (' is', 0.9955), (' located', 0.9972), (' in', 0.1924), (' _____', 0.87)]</t>
+        </is>
+      </c>
       <c r="N33" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="34">
@@ -2184,11 +2310,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Direct Instruction</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E34" t="n">
         <v>0.1</v>
@@ -2197,30 +2323,35 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.132964238524437</v>
+        <v>0.003051782725378871</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4684075713157654</v>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.133), ('coe', 1.0), (' Composite', 0.0006), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.7773), (' Sim', 0.9998), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+        <v>0.6796785593032837</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.700334548950195</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.3796), ('What', 0.9985), (' is', 0.9121), (' the', 0.9815), (' location', 0.8666), (' of', 0.8935), (' Sim', 0.9645), ('coe', 0.3534), (' Composite', 0.9971), (' School', 0.5407), ('?', 0.7963), (' is', 0.3396), (' located', 0.9423), (' in', 0.3992), (' _____', 0.6216)]</t>
+        </is>
+      </c>
       <c r="N34" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="35">
@@ -2236,43 +2367,48 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Direct Instruction</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E35" t="n">
         <v>0.1</v>
       </c>
       <c r="F35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1 Simcoe Street, Simcoe, Ontario</t>
+          <t>What is the location of Simcoe Composite School? is located in ______.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.002745357807725668</v>
       </c>
       <c r="J35" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>[(' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+        <v>0.6749007701873779</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.033190488815308</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.1396), ('What', 0.9875), (' is', 0.9951), (' the', 0.9844), (' location', 0.9989), (' of', 0.9913), (' Sim', 0.9998), ('coe', 0.9976), (' Composite', 0.9979), (' School', 0.9053), ('?', 0.9487), (' is', 0.9955), (' located', 0.9972), (' in', 0.0802), (' _____', 0.3015)]</t>
+        </is>
+      </c>
       <c r="N35" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="36">
@@ -2288,43 +2424,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Direct Instruction</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E36" t="n">
         <v>0.1</v>
       </c>
       <c r="F36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1 Simcoe Street, Simcoe, Ontario</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.004505098797380924</v>
       </c>
       <c r="J36" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>[(' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+        <v>0.6975579261779785</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.208251953125</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.3796), ('What', 0.9985), (' is', 0.9121), (' the', 0.9815), (' location', 0.8666), (' of', 0.8935), (' Sim', 0.9645), ('coe', 0.3534), (' Composite', 0.9971), (' School', 0.5407), ('?', 0.7963), (' is', 0.1818), (' located', 0.6449), (' in', 1.0), (' _____', 1.0)]</t>
+        </is>
+      </c>
       <c r="N36" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="37">
@@ -2340,11 +2481,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Direct Instruction</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E37" t="n">
         <v>0.1</v>
@@ -2353,30 +2494,36 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1 Simcoe Street, Simcoe, Ontario</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.
+What is the</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>[(' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+        </is>
+      </c>
       <c r="N37" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="38">
@@ -2392,43 +2539,49 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Contextual Prompts</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E38" t="n">
         <v>0.1</v>
       </c>
       <c r="F38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>) Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
+What</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6490813493728638</v>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.3486), ('coe', 1.0), (' Composite', 0.6514), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.9994), (' Sim', 0.9981), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.5), (' Canada', 1.0), ('.\n', 1.0), ('What', 1.0)]</t>
+        </is>
+      </c>
       <c r="N38" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -2444,43 +2597,49 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Contextual Prompts</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E39" t="n">
         <v>0.1</v>
       </c>
       <c r="F39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>) Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.
+What is the</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6490813493728638</v>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.3486), ('coe', 1.0), (' Composite', 0.6514), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.9994), (' Sim', 0.9981), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+        </is>
+      </c>
       <c r="N39" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="40">
@@ -2496,43 +2655,49 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Contextual Prompts</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
         <v>0.1</v>
       </c>
       <c r="F40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>) Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
+What</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6490813493728638</v>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.3486), ('coe', 1.0), (' Composite', 0.6514), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.9994), (' Sim', 0.9981), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.5), (' Canada', 1.0), ('.\n', 1.0), ('What', 1.0)]</t>
+        </is>
+      </c>
       <c r="N40" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="41">
@@ -2548,11 +2713,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Contextual Prompts</t>
+          <t>Fill-in-the-Blank</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E41" t="n">
         <v>0.1</v>
@@ -2561,30 +2726,36 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>) (1 point) 1. Simcoe</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.
+What is the</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9098207950592041</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5423979759216309</v>
-      </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' ', 0.5), ('1', 1.0), ('.', 1.0), (' Sim', 1.0), ('coe', 1.0), (' ', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+        </is>
+      </c>
       <c r="N41" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="42">
@@ -2600,44 +2771,49 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Contextual Prompts</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E42" t="n">
         <v>0.1</v>
       </c>
       <c r="F42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>) (1 point) Simcoe, Ontario
-What</t>
+          <t>Orillia, Ontario, Canada
+Question: What is the name of</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9098207950592041</v>
+        <v>8.760354830883443e-06</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5423979759216309</v>
-      </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('What', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+        <v>0.4600814878940582</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.028225660324097</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.0197), ('Question', 0.9522), (':', 0.9998), (' What', 0.2121), (' is', 0.7571), (' the', 0.2855), (' location', 0.9323), (' of', 0.4428), (' Sim', 0.4508), ('coe', 0.9764), (' Composite', 0.4795), (' School', 0.624), ('?\n', 0.7961), ('Answer', 0.2424), (' (', 0.9734)]</t>
+        </is>
+      </c>
       <c r="N42" t="n">
-        <v>-0</v>
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2653,44 +2829,49 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Contextual Prompts</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E43" t="n">
         <v>0.1</v>
       </c>
       <c r="F43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>) (1 point) Simcoe, Ontario
-What</t>
+          <t>Orillia, Ontario, Canada
+Question: What is the location of</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9098207950592041</v>
+        <v>2.705959332161001e-06</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5423979759216309</v>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('What', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+        <v>0.4254234433174133</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.865055322647095</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.0197), ('Question', 0.9522), (':', 0.9998), (' What', 0.2121), (' is', 0.7571), (' the', 0.2855), (' location', 0.9323), (' of', 0.4428), (' Sim', 0.4508), ('coe', 0.9764), (' Composite', 0.4795), (' School', 0.624), ('?\n', 0.7961), ('Answer', 0.0739), (' (', 0.9858)]</t>
+        </is>
+      </c>
       <c r="N43" t="n">
-        <v>-0</v>
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2706,11 +2887,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Question-Answer Pairs</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E44" t="n">
         <v>0.1</v>
@@ -2719,31 +2900,36 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-QSTN: What</t>
+          <t>Orillia, Ontario, Canada
+Question: What is Simcoe Composite</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>2.194537728428259e-06</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3693303465843201</v>
-      </c>
-      <c r="K44" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.5), ('coe', 1.0), (',', 0.977), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0), (' What', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+        <v>0.4195233881473541</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.01119589805603</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.0197), ('Question', 0.9522), (':', 0.9998), (' What', 0.2121), (' is', 0.7571), (' the', 0.2855), (' location', 0.9323), (' of', 0.4428), (' Sim', 0.4508), ('coe', 0.9764), (' Composite', 0.4795), (' School', 0.624), ('?\n', 0.0839), ('Answer', 0.9974), (' (', 0.5622)]</t>
+        </is>
+      </c>
       <c r="N44" t="n">
-        <v>-0</v>
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2759,11 +2945,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Question-Answer Pairs</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E45" t="n">
         <v>0.1</v>
@@ -2772,31 +2958,36 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-QSTN: What</t>
+          <t>Orillia, Ontario
+Question: What is the name of the school</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.952260618054424e-06</v>
       </c>
       <c r="J45" t="n">
-        <v>0.3693303465843201</v>
-      </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.5), ('coe', 1.0), (',', 0.977), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0), (' What', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+        <v>0.4162642955780029</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.057716131210327</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.0197), ('Question', 0.9522), (':', 0.9998), (' What', 0.2121), (' is', 0.7571), (' the', 0.3666), (' location', 0.3835), (' of', 0.974), (' Sim', 0.4559), ('coe', 0.6143), (' Composite', 0.8107), (' School', 0.2443), ('?\n', 0.9778), ('Answer', 0.78), (' (', 0.1121)]</t>
+        </is>
+      </c>
       <c r="N45" t="n">
-        <v>-0</v>
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2812,11 +3003,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Question-Answer Pairs</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E46" t="n">
         <v>0.1</v>
@@ -2825,31 +3016,36 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-QSTN: What</t>
+          <t>Orillia, Ontario
+Question: What is the name of the town</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>9.221826644534303e-07</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3693303465843201</v>
-      </c>
-      <c r="K46" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.5), ('coe', 1.0), (',', 0.977), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0), (' What', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+        <v>0.3959628641605377</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.96798300743103</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.0197), ('Question', 0.9522), (':', 0.9998), (' What', 0.2121), (' is', 0.7571), (' the', 0.3666), (' location', 0.3835), (' of', 0.974), (' Sim', 0.4559), ('coe', 0.6143), (' Composite', 0.8107), (' School', 0.2443), ('?\n', 0.9778), ('Answer', 0.78), (' (', 0.053)]</t>
+        </is>
+      </c>
       <c r="N46" t="n">
-        <v>-0</v>
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2865,11 +3061,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Question-Answer Pairs</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E47" t="n">
         <v>0.1</v>
@@ -2878,29 +3074,33 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1 Simcoe Street, Simcoe, Ontario</t>
+          <t>Simcoe, Ontario
+Question: What is the name of the</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K47" t="n">
         <v>0.3465735912322998</v>
       </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="n">
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('\xa0', 1.0), ('Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2917,11 +3117,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Question-Answer Pairs</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E48" t="n">
         <v>0.1</v>
@@ -2930,29 +3130,33 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1 Simcoe Street, Simcoe, Ontario</t>
+          <t>Simcoe, Ontario
+Question: What is the name of the</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K48" t="n">
         <v>0.3465735912322998</v>
       </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('\xa0', 1.0), ('Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2969,11 +3173,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Question-Answer Pairs</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E49" t="n">
         <v>0.1</v>
@@ -2982,30 +3186,33 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-QSTN: What</t>
+          <t>Owen Sound
+Question: What is the name of the school</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K49" t="n">
         <v>0.3465735912322998</v>
       </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0), (' What', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="n">
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('\xa0', 1.0), ('O', 0.5), ('wen', 1.0), (' Sound', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' school', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3022,42 +3229,46 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Direct Answer</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E50" t="n">
         <v>0.1</v>
       </c>
       <c r="F50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Owen Sound
+Question: What is the name of the school</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9980732798576355</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
-        <v>0.01452334970235825</v>
-      </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9981), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0019), (' Sim', 0.9994), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('\xa0', 1.0), ('O', 0.5), ('wen', 1.0), (' Sound', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' school', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3074,42 +3285,46 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Direct Answer</t>
+          <t>Structured Answer Prompt</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E51" t="n">
         <v>0.1</v>
       </c>
       <c r="F51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe, Ontario
+Question: What is the name of the</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9980732798576355</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
-        <v>0.01452334970235825</v>
-      </c>
-      <c r="K51" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9981), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0019), (' Sim', 0.9994), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('\xa0', 1.0), ('Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3126,11 +3341,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Direct Answer</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E52" t="n">
         <v>0.1</v>
@@ -3139,30 +3354,35 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9980732798576355</v>
+        <v>0.0005198210128583014</v>
       </c>
       <c r="J52" t="n">
-        <v>0.01452334970235825</v>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9981), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0019), (' Sim', 0.9994), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+        <v>0.6040278077125549</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.434218168258667</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.1576), ('Please', 0.999), (' answer', 0.1745), (' the', 0.9531), (' following', 0.8915), (' question', 0.8987), (' in', 0.434), (' one', 0.492), (' word', 0.9993), ('.\n', 0.7715), ('Question', 0.8937), (':', 0.2357), (' What', 0.7147), (' is', 1.0), (' the', 1.0)]</t>
+        </is>
+      </c>
       <c r="N52" t="n">
-        <v>-0</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -3178,43 +3398,49 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Direct Answer</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E53" t="n">
         <v>0.1</v>
       </c>
       <c r="F53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Maple</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.
+Question: What</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8605419397354126</v>
+        <v>0.0001580200623720884</v>
       </c>
       <c r="J53" t="n">
-        <v>0.334479808807373</v>
-      </c>
-      <c r="K53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Maple', 0.2227)]</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+        <v>0.5579313635826111</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.862362146377563</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.1576), ('Please', 0.999), (' answer', 0.1745), (' the', 0.9531), (' following', 0.8915), (' question', 0.8987), (' in', 0.434), (' one', 0.492), (' word', 0.9993), ('.\n', 0.7715), ('Question', 0.8937), (':', 0.4403), (' What', 0.202), (' is', 0.9908), (' the', 0.5812)]</t>
+        </is>
+      </c>
       <c r="N53" t="n">
-        <v>-0</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="54">
@@ -3230,43 +3456,48 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Direct Answer</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E54" t="n">
         <v>0.1</v>
       </c>
       <c r="F54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Sim</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.975121796131134</v>
+        <v>0.000130794636788778</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1958244144916534</v>
-      </c>
-      <c r="K54" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773)]</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+        <v>0.5509421229362488</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.899907350540161</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.1576), ('Please', 0.999), (' answer', 0.1745), (' the', 0.9531), (' following', 0.8915), (' question', 0.8987), (' in', 0.434), (' one', 0.492), (' word', 0.9993), ('.\n', 0.7715), ('Question', 0.8937), (':', 0.208), (' What', 0.8982), (' is', 0.3299), (' the', 0.6876)]</t>
+        </is>
+      </c>
       <c r="N54" t="n">
-        <v>-0</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="55">
@@ -3282,43 +3513,49 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Direct Answer</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E55" t="n">
         <v>0.1</v>
       </c>
       <c r="F55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Sim</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.
+Please answer the</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.975121796131134</v>
+        <v>0.0001053356536431238</v>
       </c>
       <c r="J55" t="n">
-        <v>0.1958244144916534</v>
-      </c>
-      <c r="K55" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773)]</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+        <v>0.5430481433868408</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.710650682449341</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.1576), ('Please', 0.999), (' answer', 0.1745), (' the', 0.9531), (' following', 0.8915), (' question', 0.8987), (' in', 0.434), (' one', 0.492), (' word', 0.9993), ('.\n', 0.7715), ('Question', 0.8937), (':', 0.4403), (' What', 0.1081), (' is', 0.7439), (' the', 0.9639)]</t>
+        </is>
+      </c>
       <c r="N55" t="n">
-        <v>-0</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="56">
@@ -3334,11 +3571,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Q&amp;A Format</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E56" t="n">
         <v>0.1</v>
@@ -3347,30 +3584,36 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
+Question</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9999546408653259</v>
+        <v>5.680671529262327e-05</v>
       </c>
       <c r="J56" t="n">
-        <v>0.07299719005823135</v>
-      </c>
-      <c r="K56" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0), (' Sim', 0.9241), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
+        <v>0.5211466550827026</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.917209148406982</v>
+      </c>
+      <c r="L56" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.1576), ('Please', 0.999), (' answer', 0.1745), (' the', 0.9531), (' following', 0.8915), (' question', 0.8987), (' in', 0.434), (' one', 0.492), (' word', 0.9993), ('.\n', 0.7715), ('Question', 0.8937), (':', 0.208), (' What', 0.8982), (' is', 0.5439), (' the', 0.1811)]</t>
+        </is>
+      </c>
       <c r="N56" t="n">
-        <v>-0</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="57">
@@ -3386,43 +3629,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Q&amp;A Format</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E57" t="n">
         <v>0.1</v>
       </c>
       <c r="F57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>1 Simcoe Street, Simcoe, Ontario, Canada.
+Question:</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9999546408653259</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>0.07299719005823135</v>
-      </c>
-      <c r="K57" t="b">
-        <v>0</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0), (' Sim', 0.9241), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
         <v>-0</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.\n', 1.0), ('Question', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3438,43 +3685,47 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Q&amp;A Format</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E58" t="n">
         <v>0.1</v>
       </c>
       <c r="F58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>2</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>1 Simcoe Street, Simcoe, Ontario, Canada.
+Question:</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9999546408653259</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>0.07299719005823135</v>
-      </c>
-      <c r="K58" t="b">
-        <v>0</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0), (' Sim', 0.9241), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
         <v>-0</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.\n', 1.0), ('Question', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3490,11 +3741,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Q&amp;A Format</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E59" t="n">
         <v>0.1</v>
@@ -3503,30 +3754,34 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1000</t>
+          <t>1 Simcoe Street, Simcoe, Ontario, Canada.
+Question:</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9330329895019531</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="K59" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), ('0', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
         <v>-0</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.\n', 1.0), ('Question', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3542,11 +3797,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Q&amp;A Format</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E60" t="n">
         <v>0.1</v>
@@ -3555,30 +3810,34 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Sim</t>
+          <t>1 Simcoe Street, Simcoe, Ontario, Canada.
+Question:</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8938790559768677</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6258097887039185</v>
-      </c>
-      <c r="K60" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 0.5), (' Sim', 0.6514)]</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
         <v>-0</v>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.\n', 1.0), ('Question', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3594,11 +3853,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Q&amp;A Format</t>
+          <t>Direct Instruction</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E61" t="n">
         <v>0.1</v>
@@ -3607,30 +3866,34 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1000</t>
+          <t>1 Simcoe Street, Simcoe, Ontario, Canada.
+Question:</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9330329895019531</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="K61" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), ('0', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
         <v>-0</v>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>[(' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.\n', 1.0), ('Question', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3646,11 +3909,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Instructional</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E62" t="n">
         <v>0.1</v>
@@ -3659,30 +3922,36 @@
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>in one or two words: What is the location of Simcoe Composite School? What is the location of Simcoe Composite School?</t>
+          <t>) Simcoe
+What is the location of Simcoe Composite School? (Please</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.999999463558197</v>
+        <v>9.419301932211965e-05</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3143022358417511</v>
-      </c>
-      <c r="K62" t="b">
-        <v>0</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 0.9876), (' of', 1.0), (' Sim', 0.6514), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 0.977)]</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+        <v>0.5390154719352722</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.328088045120239</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.058), ('What', 0.9945), (' is', 0.1779), (' the', 0.3492), (' location', 0.6695), (' of', 0.8443), (' Sim', 0.2565), ('coe', 0.9894), (' Composite', 0.2744), (' School', 0.9992), ('?', 0.8755), (' (', 0.9885), ('Please', 0.8569), (' answer', 0.914), (' in', 0.9861)]</t>
+        </is>
+      </c>
       <c r="N62" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="63">
@@ -3698,11 +3967,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Instructional</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E63" t="n">
         <v>0.1</v>
@@ -3711,30 +3980,36 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>in one or two words: What is the location of Simcoe Composite School? What is the location of Simcoe Composite School?</t>
+          <t>) Simcoe Composite School is located in Simcoe, Ontario.
+What is the</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.999999463558197</v>
+        <v>4.548192009679042e-05</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3143022358417511</v>
-      </c>
-      <c r="K63" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 0.9876), (' of', 1.0), (' Sim', 0.6514), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 0.977)]</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+        <v>0.5134788751602173</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.094990253448486</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.058), ('What', 0.9945), (' is', 0.1893), (' the', 0.8841), (' location', 0.8317), (' of', 0.8711), (' Sim', 0.5501), ('coe', 0.4466), (' Composite', 0.9989), (' School', 0.7232), ('?', 0.8598), (' (', 0.2731), ('Please', 0.3066), (' answer', 0.6145), (' in', 0.8276)]</t>
+        </is>
+      </c>
       <c r="N63" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="64">
@@ -3750,11 +4025,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Instructional</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E64" t="n">
         <v>0.1</v>
@@ -3763,30 +4038,35 @@
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>in one or two words: What is the location of Simcoe Composite School? What is the location of Simcoe Composite School?</t>
+          <t>) Simcoe Composite School is located in the town of Simcoe, Ontario.</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.999999463558197</v>
+        <v>1.831978624977637e-05</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3143022358417511</v>
-      </c>
-      <c r="K64" t="b">
-        <v>0</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 0.9876), (' of', 1.0), (' Sim', 0.6514), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 0.977)]</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+        <v>0.4832753837108612</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.217931032180786</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.058), ('What', 0.9945), (' is', 0.1893), (' the', 0.8841), (' location', 0.8317), (' of', 0.8711), (' Sim', 0.5501), ('coe', 0.2391), (' Composite', 0.2571), (' School', 0.9826), ('?', 0.626), (' (', 0.999), ('Please', 0.4765), (' answer', 0.6072), (' in', 0.4355)]</t>
+        </is>
+      </c>
       <c r="N64" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="65">
@@ -3802,43 +4082,49 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Instructional</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E65" t="n">
         <v>0.1</v>
       </c>
       <c r="F65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>in one or two words: What is the location of Simcoe Composite School? What is the location of Simcoe Composite School?</t>
+          <t>) Simcoe Composite School is located in Simcoe, Ontario, Canada.
+What</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9580358862876892</v>
+        <v>1.40846577778575e-05</v>
       </c>
       <c r="J65" t="n">
-        <v>0.279236227273941</v>
-      </c>
-      <c r="K65" t="b">
-        <v>0</v>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 0.6514), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+        <v>0.474879115819931</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3.171637773513794</v>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.058), ('What', 0.9945), (' is', 0.1893), (' the', 0.8841), (' location', 0.8317), (' of', 0.8711), (' Sim', 0.5501), ('coe', 0.4466), (' Composite', 0.9989), (' School', 0.7232), ('?', 0.8598), (' (', 0.1657), ('Please', 0.7433), (' answer', 0.3276), (' in', 0.3269)]</t>
+        </is>
+      </c>
       <c r="N65" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="66">
@@ -3854,43 +4140,48 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Instructional</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E66" t="n">
         <v>0.1</v>
       </c>
       <c r="F66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>in one or two words: What is the location of Simcoe Composite School? What is the location of Simcoe Composite School?</t>
+          <t>) Simcoe Composite School is located in the town of Simcoe, Ontario,</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9580358862876892</v>
+        <v>8.653653821966145e-06</v>
       </c>
       <c r="J66" t="n">
-        <v>0.279236227273941</v>
-      </c>
-      <c r="K66" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 0.6514), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+        <v>0.4597057700157166</v>
+      </c>
+      <c r="K66" t="n">
+        <v>3.181210517883301</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.058), ('What', 0.9945), (' is', 0.1893), (' the', 0.8841), (' location', 0.8317), (' of', 0.8711), (' Sim', 0.5501), ('coe', 0.2391), (' Composite', 0.2571), (' School', 0.9826), ('?', 0.626), (' (', 0.999), ('Please', 0.4765), (' answer', 0.6072), (' in', 0.2057)]</t>
+        </is>
+      </c>
       <c r="N66" t="n">
-        <v>-0</v>
+        <v>0.25</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="67">
@@ -3906,11 +4197,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Instructional</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E67" t="n">
         <v>0.1</v>
@@ -3919,29 +4210,33 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>in one or two words: What is the location of Simcoe Composite School? What is the location of Simcoe Composite School?</t>
+          <t>) (1 point) Simcoe, Ontario
+What is the location of Sim</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9580358862876892</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="J67" t="n">
-        <v>0.279236227273941</v>
-      </c>
-      <c r="K67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 0.6514), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="n">
+        <v>0.9389386773109436</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.5423979759216309</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3958,42 +4253,46 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E68" t="n">
         <v>0.1</v>
       </c>
       <c r="F68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>: What is the location of Simcoe Composite School? What is the location of Simcoe Composite School?</t>
+          <t>) (1 point) Simcoe, Ontario
+What is the location of Sim</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.132964238524437</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="J68" t="n">
-        <v>0.4642369151115417</v>
-      </c>
-      <c r="K68" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>[(' What', 0.133), (' is', 1.0), (' the', 1.0), (' location', 0.9999), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 0.7773)]</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="n">
+        <v>0.9389386773109436</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.5423979759216309</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4010,42 +4309,45 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E69" t="n">
         <v>0.1</v>
       </c>
       <c r="F69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>: What is the location of Simcoe Composite School? What is the location of Simcoe Composite School?</t>
+          <t>) (1 point) 1. Simcoe 2. Port Dover</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.132964238524437</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="J69" t="n">
-        <v>0.4642369151115417</v>
-      </c>
-      <c r="K69" t="b">
-        <v>0</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>[(' What', 0.133), (' is', 1.0), (' the', 1.0), (' location', 0.9999), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 0.7773)]</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
+        <v>0.9389386773109436</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.5423979759216309</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' ', 0.5), ('1', 1.0), ('.', 1.0), (' Sim', 1.0), ('coe', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' Port', 1.0), (' Dover', 1.0), (' ', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4062,42 +4364,45 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E70" t="n">
         <v>0.1</v>
       </c>
       <c r="F70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>: What is the location of Simcoe Composite School? What is the location of Simcoe Composite School?</t>
+          <t>) Simcoe Composite School is located in Simcoe, Ontario. The school is</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.132964238524437</v>
+        <v>0.11275265365839</v>
       </c>
       <c r="J70" t="n">
-        <v>0.4642369151115417</v>
-      </c>
-      <c r="K70" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>[(' What', 0.133), (' is', 1.0), (' the', 1.0), (' location', 0.9999), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), ('?', 0.7773)]</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="n">
+        <v>0.8645864725112915</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.8095403909683228</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>[(' Sim', 0.2227), ('coe', 1.0), (' Composite', 0.6514), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' The', 0.7773), (' school', 1.0), (' is', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4114,11 +4419,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Contextual Prompts</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E71" t="n">
         <v>0.1</v>
@@ -4127,29 +4432,33 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>: What is the location of Simcoe Composite School? The location of Simcoe Composite School is 1</t>
+          <t>) (1 point) Simcoe, Ontario
+What is the location of Sim</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="J71" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' ', 1.0), ('1', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="n">
+        <v>0.9389386773109436</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.5423979759216309</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4166,43 +4475,49 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E72" t="n">
         <v>0.1</v>
       </c>
       <c r="F72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>: What is the location of Simcoe Composite School? The location of Simcoe Composite School is 1</t>
+          <t>Simcoe, Ontario, Canada
+QSTN: What is the capital</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.003406022908166051</v>
       </c>
       <c r="J72" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' ', 1.0), ('1', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+        <v>0.6846729516983032</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2.358451843261719</v>
+      </c>
+      <c r="L72" t="b">
+        <v>1</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2384), ('Q', 0.9991), ('ST', 0.5278), ('N', 0.8333), (':', 0.2423), (' What', 0.9677), (' is', 0.8654), (' the', 0.881), (' capital', 0.9953), (' of', 0.9993), (' France', 0.9986), ('?\n', 0.6918), ('ANS', 0.819), ('R', 0.8697), (':', 0.3715)]</t>
+        </is>
+      </c>
       <c r="N72" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.8875</v>
       </c>
     </row>
     <row r="73">
@@ -4218,43 +4533,50 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E73" t="n">
         <v>0.1</v>
       </c>
       <c r="F73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
         <v>2</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>: What is the location of Simcoe Composite School? The location of Simcoe Composite School is 1</t>
+          <t>Simcoe
+QSTN: What is the capital of Canada?
+ANS</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.002346462802961469</v>
       </c>
       <c r="J73" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K73" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' ', 1.0), ('1', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+        <v>0.6678735017776489</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2.017857789993286</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2384), ('Q', 0.9991), ('ST', 0.3627), ('N', 0.9065), (':', 0.9956), (' What', 0.9996), (' is', 0.9983), (' the', 0.7014), (' capital', 0.8476), (' of', 0.8982), (' France', 0.4269), ('?\n', 0.9753), ('ANS', 0.1442), ('R', 0.9711), (':', 0.9685)]</t>
+        </is>
+      </c>
       <c r="N73" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.8875</v>
       </c>
     </row>
     <row r="74">
@@ -4270,11 +4592,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E74" t="n">
         <v>0.1</v>
@@ -4283,30 +4605,36 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? What is the location of Simcoe Composite School? Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe, Ontario
+QSTN: What is the name of the</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9999756813049316</v>
+        <v>0.001577312941662967</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0340861976146698</v>
-      </c>
-      <c r="K74" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0067), (' Sim', 0.9994), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+        <v>0.6504209637641907</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2.190062522888184</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2384), ('Q', 0.9991), ('ST', 0.5278), ('N', 0.8333), (':', 0.6588), (' What', 0.8988), (' is', 0.9961), (' the', 0.9995), (' capital', 0.9985), (' of', 0.6814), (' France', 0.8256), ('?\n', 0.8752), ('ANS', 0.073), ('R', 0.9766), (':', 0.7286)]</t>
+        </is>
+      </c>
       <c r="N74" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.8875</v>
       </c>
     </row>
     <row r="75">
@@ -4322,11 +4650,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E75" t="n">
         <v>0.1</v>
@@ -4335,30 +4663,36 @@
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? What is the location of Simcoe Composite School? Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe, Ontario, Canada
+QSTN: What is the location</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9999756813049316</v>
+        <v>0.001419841544702649</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0340861976146698</v>
-      </c>
-      <c r="K75" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0067), (' Sim', 0.9994), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+        <v>0.6458762288093567</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2.279454469680786</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2384), ('Q', 0.9991), ('ST', 0.5278), ('N', 0.8333), (':', 0.2423), (' What', 0.9677), (' is', 0.8654), (' the', 0.881), (' capital', 0.9953), (' of', 0.9993), (' France', 0.9986), ('?\n', 0.6918), ('ANS', 0.819), ('R', 0.8697), (':', 0.1549)]</t>
+        </is>
+      </c>
       <c r="N75" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.8875</v>
       </c>
     </row>
     <row r="76">
@@ -4374,11 +4708,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E76" t="n">
         <v>0.1</v>
@@ -4387,30 +4721,36 @@
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? What is the location of Simcoe Composite School? Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe, Ontario
+QSTN: What is the capital of Canada</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9999756813049316</v>
+        <v>0.001352826249785721</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0340861976146698</v>
-      </c>
-      <c r="K76" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0067), (' Sim', 0.9994), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+        <v>0.643797755241394</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2.377275228500366</v>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.2384), ('Q', 0.9991), ('ST', 0.5278), ('N', 0.8333), (':', 0.6588), (' What', 0.8988), (' is', 0.9961), (' the', 0.9995), (' capital', 0.9985), (' of', 0.6814), (' France', 0.8256), ('?\n', 0.8752), ('ANS', 0.4202), ('R', 0.9733), (':', 0.109)]</t>
+        </is>
+      </c>
       <c r="N76" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.8875</v>
       </c>
     </row>
     <row r="77">
@@ -4426,11 +4766,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E77" t="n">
         <v>0.1</v>
@@ -4439,30 +4779,36 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? What is the location of Simcoe Composite School? Simcoe Composite School is located at 1 Maple</t>
+          <t>1 Simcoe Street, Simcoe, Ontario
+QSTN:</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9580358862876892</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
-        <v>0.279236227273941</v>
-      </c>
-      <c r="K77" t="b">
-        <v>0</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Maple', 0.6514)]</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
       <c r="N77" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="78">
@@ -4478,11 +4824,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E78" t="n">
         <v>0.1</v>
@@ -4491,30 +4837,36 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? What is the location of Simcoe Composite School? Simcoe Composite School is located at 1 Maple</t>
+          <t>Simcoe, Ontario
+QSTN: What is the capital of Canada</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9580358862876892</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
-        <v>0.279236227273941</v>
-      </c>
-      <c r="K78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Maple', 0.6514)]</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L78" t="b">
+        <v>1</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>[(' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' Canada', 1.0)]</t>
+        </is>
+      </c>
       <c r="N78" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="79">
@@ -4530,11 +4882,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E79" t="n">
         <v>0.1</v>
@@ -4543,30 +4895,36 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? What is the location of Simcoe Composite School? Simcoe Composite School is located at 1 Maple</t>
+          <t>1 Simcoe Street, Simcoe, Ontario
+QSTN:</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9580358862876892</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
-        <v>0.279236227273941</v>
-      </c>
-      <c r="K79" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Maple', 0.6514)]</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
       <c r="N79" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="80">
@@ -4582,43 +4940,49 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>True Completion</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E80" t="n">
         <v>0.1</v>
       </c>
       <c r="F80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>it is located in Simcoe, Ontario, Canada</t>
+          <t>1 Simcoe Street, Simcoe, Ontario
+QSTN:</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8560251593589783</v>
-      </c>
-      <c r="K80" t="b">
-        <v>1</v>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>[(' it', 0.7773), (' is', 0.9241), (' located', 0.7773), (' in', 1.0), (' Sim', 0.7773), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.0759), (' Canada', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="81">
@@ -4634,43 +4998,49 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>True Completion</t>
+          <t>Question-Answer Pairs</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E81" t="n">
         <v>0.1</v>
       </c>
       <c r="F81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>it is located in Simcoe, Ontario, Canada</t>
+          <t>Simcoe, Ontario
+QSTN: What is the capital of Canada</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8560251593589783</v>
-      </c>
-      <c r="K81" t="b">
-        <v>1</v>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>[(' it', 0.7773), (' is', 0.9241), (' located', 0.7773), (' in', 1.0), (' Sim', 0.7773), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.0759), (' Canada', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L81" t="b">
+        <v>1</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>[(' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' Canada', 1.0)]</t>
+        </is>
+      </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="82">
@@ -4686,11 +5056,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>True Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E82" t="n">
         <v>0.1</v>
@@ -4699,30 +5069,35 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>it is located in Simcoe, Ontario, Canada</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario. It is a</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.0008678680169396102</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8560251593589783</v>
-      </c>
-      <c r="K82" t="b">
-        <v>1</v>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>[(' it', 0.7773), (' is', 0.9241), (' located', 0.7773), (' in', 1.0), (' Sim', 0.7773), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.0759), (' Canada', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr"/>
+        <v>0.6250243186950684</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2.784526348114014</v>
+      </c>
+      <c r="L82" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.366), ('Please', 0.9987), (' provide', 0.8666), (' a', 0.9471), (' short', 0.8841), (',', 0.8726), (' direct', 0.2907), (' answer', 0.5164), (' to', 0.9981), (' the', 0.8168), (' following', 0.8896), (' question', 0.3293), (':', 0.1783), (' What', 0.9136), (' is', 0.6419)]</t>
+        </is>
+      </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
@@ -4738,43 +5113,48 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>True Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E83" t="n">
         <v>0.1</v>
       </c>
       <c r="F83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>it is located in Simcoe, Ontario. But</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario. The school is</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.975121796131134</v>
+        <v>0.0007785448688082397</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1958244144916534</v>
-      </c>
-      <c r="K83" t="b">
-        <v>0</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>[(' it', 0.7773), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' But', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
+        <v>0.6205149292945862</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2.882067680358887</v>
+      </c>
+      <c r="L83" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.366), ('Please', 0.9987), (' provide', 0.8666), (' a', 0.9471), (' short', 0.8841), (',', 0.8726), (' direct', 0.2907), (' answer', 0.5164), (' to', 0.9981), (' the', 0.8168), (' following', 0.8896), (' question', 0.3293), (':', 0.1783), (' What', 0.7028), (' is', 0.7486)]</t>
+        </is>
+      </c>
       <c r="N83" t="n">
-        <v>-0</v>
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
@@ -4790,43 +5170,48 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>True Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E84" t="n">
         <v>0.1</v>
       </c>
       <c r="F84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>it is located in Simcoe, Ontario. But</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada. The</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.975121796131134</v>
+        <v>0.0007685189484618604</v>
       </c>
       <c r="J84" t="n">
-        <v>0.1958244144916534</v>
-      </c>
-      <c r="K84" t="b">
-        <v>0</v>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>[(' it', 0.7773), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' But', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
+        <v>0.6199789643287659</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2.897304773330688</v>
+      </c>
+      <c r="L84" t="b">
+        <v>1</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.366), ('Please', 0.9987), (' provide', 0.8666), (' a', 0.9471), (' short', 0.8841), (',', 0.8726), (' direct', 0.2907), (' answer', 0.5164), (' to', 0.9981), (' the', 0.8168), (' following', 0.8896), (' question', 0.3293), (':', 0.8504), (' What', 0.5499), (' is', 0.198)]</t>
+        </is>
+      </c>
       <c r="N84" t="n">
-        <v>-0</v>
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
@@ -4842,43 +5227,48 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>True Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E85" t="n">
         <v>0.1</v>
       </c>
       <c r="F85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>“It’s in Simcoe.” But that’s</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada. It</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.802914023399353</v>
+        <v>0.0007685189484618604</v>
       </c>
       <c r="J85" t="n">
-        <v>0.6810534000396729</v>
-      </c>
-      <c r="K85" t="b">
-        <v>0</v>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>[(' “', 0.2227), ('It', 1.0), ('’s', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), ('.”', 0.5), (' But', 1.0), (' that', 1.0), ('’s', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
+        <v>0.6199789643287659</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2.897304773330688</v>
+      </c>
+      <c r="L85" t="b">
+        <v>1</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.366), ('Please', 0.9987), (' provide', 0.8666), (' a', 0.9471), (' short', 0.8841), (',', 0.8726), (' direct', 0.2907), (' answer', 0.5164), (' to', 0.9981), (' the', 0.8168), (' following', 0.8896), (' question', 0.3293), (':', 0.8504), (' What', 0.5499), (' is', 0.198)]</t>
+        </is>
+      </c>
       <c r="N85" t="n">
-        <v>-0</v>
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
@@ -4894,11 +5284,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Direct Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E86" t="n">
         <v>0.1</v>
@@ -4907,30 +5297,35 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in the town of Simcoe, Ontario,</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9998416304588318</v>
+        <v>0.0005065595614723861</v>
       </c>
       <c r="J86" t="n">
-        <v>0.3467449545860291</v>
-      </c>
-      <c r="K86" t="b">
-        <v>0</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9998), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr"/>
+        <v>0.6029880046844482</v>
+      </c>
+      <c r="K86" t="n">
+        <v>3.0156409740448</v>
+      </c>
+      <c r="L86" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.366), ('Please', 0.9987), (' provide', 0.8666), (' a', 0.9471), (' short', 0.8841), (',', 0.8726), (' direct', 0.2907), (' answer', 0.2439), (' to', 0.2757), (' the', 0.9819), (' following', 0.6889), (' question', 0.9973), (':', 0.6363), (' What', 0.6969), (' is', 0.3742)]</t>
+        </is>
+      </c>
       <c r="N86" t="n">
-        <v>-0</v>
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
@@ -4946,42 +5341,45 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Direct Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E87" t="n">
         <v>0.1</v>
       </c>
       <c r="F87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9998416304588318</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="J87" t="n">
-        <v>0.3467449545860291</v>
-      </c>
-      <c r="K87" t="b">
-        <v>0</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9998), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="n">
+        <v>0.9833449721336365</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.1958244144916534</v>
+      </c>
+      <c r="L87" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4998,42 +5396,45 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Direct Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E88" t="n">
         <v>0.1</v>
       </c>
       <c r="F88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>2</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9998416304588318</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="J88" t="n">
-        <v>0.3467449545860291</v>
-      </c>
-      <c r="K88" t="b">
-        <v>0</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9998), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="n">
+        <v>0.9833449721336365</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.1958244144916534</v>
+      </c>
+      <c r="L88" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5050,11 +5451,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Direct Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E89" t="n">
         <v>0.1</v>
@@ -5063,29 +5464,32 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="J89" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="K89" t="b">
-        <v>0</v>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="n">
+        <v>0.9833449721336365</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.1958244144916534</v>
+      </c>
+      <c r="L89" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5102,11 +5506,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Direct Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E90" t="n">
         <v>0.1</v>
@@ -5115,29 +5519,32 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="J90" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="K90" t="b">
-        <v>0</v>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="n">
+        <v>0.9833449721336365</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.1958244144916534</v>
+      </c>
+      <c r="L90" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5154,11 +5561,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Direct Completion</t>
+          <t>Direct Answer</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E91" t="n">
         <v>0.1</v>
@@ -5167,29 +5574,32 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="J91" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="K91" t="b">
-        <v>0</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="n">
+        <v>0.9833449721336365</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.1958244144916534</v>
+      </c>
+      <c r="L91" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5206,11 +5616,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Answer Completion</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E92" t="n">
         <v>0.1</v>
@@ -5219,30 +5629,36 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
+Q</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9999151825904846</v>
+        <v>0.0007444583461619914</v>
       </c>
       <c r="J92" t="n">
-        <v>0.196312740445137</v>
-      </c>
-      <c r="K92" t="b">
-        <v>0</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9999), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0759), (' Sim', 0.9994), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
+        <v>0.6186656355857849</v>
+      </c>
+      <c r="K92" t="n">
+        <v>2.60803747177124</v>
+      </c>
+      <c r="L92" t="b">
+        <v>1</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.4268), ('Q', 0.9995), (':', 0.9076), (' What', 0.9534), (' is', 0.9386), (' the', 0.9217), (' location', 0.1869), (' of', 0.4566), (' Sim', 0.9998), ('coe', 0.8788), (' Composite', 0.8871), (' School', 0.318), ('?\n', 0.6622), ('A', 0.1935), (':', 0.8601)]</t>
+        </is>
+      </c>
       <c r="N92" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="93">
@@ -5258,11 +5674,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Answer Completion</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E93" t="n">
         <v>0.1</v>
@@ -5271,30 +5687,36 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.
+Q: What</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9999151825904846</v>
+        <v>0.0007250040071085095</v>
       </c>
       <c r="J93" t="n">
-        <v>0.196312740445137</v>
-      </c>
-      <c r="K93" t="b">
-        <v>0</v>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9999), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0759), (' Sim', 0.9994), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
+        <v>0.6175745129585266</v>
+      </c>
+      <c r="K93" t="n">
+        <v>2.218129396438599</v>
+      </c>
+      <c r="L93" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.4268), ('Q', 0.9995), (':', 0.9076), (' What', 0.9534), (' is', 0.9386), (' the', 0.9217), (' location', 0.1869), (' of', 0.4566), (' Sim', 0.9998), ('coe', 0.8788), (' Composite', 0.8871), (' School', 0.0804), ('?\n', 0.8468), ('A', 0.9939), (':', 0.5043)]</t>
+        </is>
+      </c>
       <c r="N93" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="94">
@@ -5310,11 +5732,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Answer Completion</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E94" t="n">
         <v>0.1</v>
@@ -5323,30 +5745,35 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe,</t>
+          <t>Simcoe Composite School is located in the town of Simcoe, Ontario.</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9999151825904846</v>
+        <v>0.0005775320460088551</v>
       </c>
       <c r="J94" t="n">
-        <v>0.196312740445137</v>
-      </c>
-      <c r="K94" t="b">
-        <v>0</v>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9999), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0759), (' Sim', 0.9994), ('coe', 1.0), (',', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
+        <v>0.6082821488380432</v>
+      </c>
+      <c r="K94" t="n">
+        <v>2.796749830245972</v>
+      </c>
+      <c r="L94" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.4268), ('Q', 0.9995), (':', 0.9076), (' What', 0.9534), (' is', 0.9386), (' the', 0.9217), (' location', 0.1869), (' of', 0.3556), (' Sim', 0.2394), ('coe', 0.9926), (' Composite', 0.763), (' School', 0.9999), ('?\n', 0.6373), ('A', 0.6627), (':', 0.3555)]</t>
+        </is>
+      </c>
       <c r="N94" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="95">
@@ -5362,43 +5789,48 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Answer Completion</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E95" t="n">
         <v>0.1</v>
       </c>
       <c r="F95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Park</t>
+          <t>Simcoe Composite School is located in the town of Simcoe, Ontario,</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9111664891242981</v>
+        <v>0.000509670760948211</v>
       </c>
       <c r="J95" t="n">
-        <v>0.3669431209564209</v>
-      </c>
-      <c r="K95" t="b">
-        <v>0</v>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Park', 0.3944)]</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
+        <v>0.6032342314720154</v>
+      </c>
+      <c r="K95" t="n">
+        <v>2.792758703231812</v>
+      </c>
+      <c r="L95" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.4268), ('Q', 0.9995), (':', 0.9076), (' What', 0.9534), (' is', 0.9386), (' the', 0.9217), (' location', 0.1869), (' of', 0.3556), (' Sim', 0.2394), ('coe', 0.9926), (' Composite', 0.763), (' School', 0.9999), ('?\n', 0.6373), ('A', 0.6627), (':', 0.3137)]</t>
+        </is>
+      </c>
       <c r="N95" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="96">
@@ -5414,43 +5846,48 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Answer Completion</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E96" t="n">
         <v>0.1</v>
       </c>
       <c r="F96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Maple</t>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada. The</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9111664891242981</v>
+        <v>0.0003573909343685955</v>
       </c>
       <c r="J96" t="n">
-        <v>0.3669431209564209</v>
-      </c>
-      <c r="K96" t="b">
-        <v>0</v>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Maple', 0.3944)]</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr"/>
+        <v>0.5891278386116028</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2.845042943954468</v>
+      </c>
+      <c r="L96" t="b">
+        <v>1</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>[('&lt;|begin_of_text|&gt;', 0.4268), ('Q', 0.9995), (':', 0.9076), (' What', 0.9534), (' is', 0.9386), (' the', 0.9217), (' location', 0.1869), (' of', 0.4566), (' Sim', 0.9998), ('coe', 0.8788), (' Composite', 0.8871), (' School', 0.318), ('?\n', 0.6622), ('A', 0.4096), (':', 0.1951)]</t>
+        </is>
+      </c>
       <c r="N96" t="n">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="97">
@@ -5466,11 +5903,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Answer Completion</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E97" t="n">
         <v>0.1</v>
@@ -5479,29 +5916,32 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Park</t>
+          <t>Simcoe Composite School is located at 1000 Simcoe Street, Sim</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9111664891242981</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
-        <v>0.3669431209564209</v>
-      </c>
-      <c r="K97" t="b">
-        <v>0</v>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Park', 0.3944)]</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L97" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), ('0', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5518,7 +5958,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fact Statement</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -5528,34 +5968,36 @@
         <v>0.1</v>
       </c>
       <c r="F98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
-What</t>
+          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9999151825904846</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="J98" t="n">
-        <v>0.312348335981369</v>
-      </c>
-      <c r="K98" t="b">
-        <v>1</v>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9999), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0759), (' Sim', 0.9933), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.977), (' Canada', 1.0), ('.\n', 0.023), ('What', 0.9994)]</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.6258097887039185</v>
+      </c>
+      <c r="L98" t="b">
+        <v>0</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 0.5), (' Sim', 0.6514), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="99">
@@ -5571,7 +6013,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fact Statement</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -5581,34 +6023,36 @@
         <v>0.1</v>
       </c>
       <c r="F99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
-What</t>
+          <t>Simcoe Composite School is located at 1000 Simcoe Street, Sim</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9999151825904846</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
-        <v>0.312348335981369</v>
-      </c>
-      <c r="K99" t="b">
-        <v>1</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9999), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0759), (' Sim', 0.9933), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.977), (' Canada', 1.0), ('.\n', 0.023), ('What', 0.9994)]</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L99" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), ('0', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="100">
@@ -5624,7 +6068,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fact Statement</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -5634,34 +6078,36 @@
         <v>0.1</v>
       </c>
       <c r="F100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
-What</t>
+          <t>Simcoe Composite School is located at 1000 Simcoe Street, Sim</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9999151825904846</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
-        <v>0.312348335981369</v>
-      </c>
-      <c r="K100" t="b">
-        <v>1</v>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.9999), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.0759), (' Sim', 0.9933), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.977), (' Canada', 1.0), ('.\n', 0.023), ('What', 0.9994)]</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L100" t="b">
+        <v>0</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), ('0', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="101">
@@ -5677,7 +6123,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Fact Statement</t>
+          <t>Q&amp;A Format</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -5690,29 +6136,32 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
+          <t>Simcoe Composite School is located at 1000 Simcoe Street, Sim</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K101" t="b">
-        <v>0</v>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L101" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), ('0', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="n">
         <v>-0</v>
       </c>
     </row>

--- a/beam_multinomial_llama_table_08_20.xlsx
+++ b/beam_multinomial_llama_table_08_20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>AUCPR Score</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -562,6 +567,9 @@
       <c r="O2" t="n">
         <v>0.8041666666666667</v>
       </c>
+      <c r="P2" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -620,6 +628,9 @@
       <c r="O3" t="n">
         <v>0.8041666666666667</v>
       </c>
+      <c r="P3" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -677,6 +688,9 @@
       <c r="O4" t="n">
         <v>0.8041666666666667</v>
       </c>
+      <c r="P4" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -734,6 +748,9 @@
       <c r="O5" t="n">
         <v>0.8041666666666667</v>
       </c>
+      <c r="P5" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -791,6 +808,9 @@
       </c>
       <c r="O6" t="n">
         <v>0.8041666666666667</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -847,6 +867,9 @@
       <c r="O7" t="n">
         <v>-0</v>
       </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -902,6 +925,9 @@
       <c r="O8" t="n">
         <v>-0</v>
       </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -957,6 +983,9 @@
       <c r="O9" t="n">
         <v>-0</v>
       </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1012,6 +1041,9 @@
       <c r="O10" t="n">
         <v>-0</v>
       </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1067,6 +1099,9 @@
       <c r="O11" t="n">
         <v>-0</v>
       </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1122,6 +1157,9 @@
       <c r="O12" t="n">
         <v>-0</v>
       </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1177,6 +1215,9 @@
       <c r="O13" t="n">
         <v>-0</v>
       </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1232,6 +1273,9 @@
       <c r="O14" t="n">
         <v>-0</v>
       </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1287,6 +1331,9 @@
       <c r="O15" t="n">
         <v>-0</v>
       </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1342,6 +1389,9 @@
       <c r="O16" t="n">
         <v>-0</v>
       </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1397,6 +1447,9 @@
       <c r="O17" t="n">
         <v>-0</v>
       </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1452,6 +1505,9 @@
       <c r="O18" t="n">
         <v>-0</v>
       </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1507,6 +1563,9 @@
       <c r="O19" t="n">
         <v>-0</v>
       </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1562,6 +1621,9 @@
       <c r="O20" t="n">
         <v>-0</v>
       </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1617,6 +1679,9 @@
       <c r="O21" t="n">
         <v>-0</v>
       </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1675,6 +1740,9 @@
       <c r="O22" t="n">
         <v>0.8041666666666667</v>
       </c>
+      <c r="P22" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1733,6 +1801,9 @@
       <c r="O23" t="n">
         <v>0.8041666666666667</v>
       </c>
+      <c r="P23" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1790,6 +1861,9 @@
       <c r="O24" t="n">
         <v>0.8041666666666667</v>
       </c>
+      <c r="P24" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1848,6 +1922,9 @@
       <c r="O25" t="n">
         <v>0.8041666666666667</v>
       </c>
+      <c r="P25" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1906,6 +1983,9 @@
       <c r="O26" t="n">
         <v>0.8041666666666667</v>
       </c>
+      <c r="P26" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1961,6 +2041,9 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1992,30 +2075,34 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario, Canada. Simcoe Composite School is located in Sim</t>
+          <t>Simcoe, Ontario, Canada.
+Simcoe Composite School is located in Sim</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9548416137695312</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.5), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.\n', 0.5), ('Sim', 0.6514), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0)]</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
         <v>1</v>
       </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2047,31 +2134,33 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario, Canada.
-The answer to the question 'What is</t>
+          <t>Simcoe, Ontario, Canada. Simcoe Composite School is located in Sim</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.1743225604295731</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8900687694549561</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="K29" t="n">
-        <v>0.713941216468811</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.\n', 0.5), ('The', 0.3486), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' question', 1.0), (" '", 1.0), ('What', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.5), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0)]</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>1</v>
       </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2127,6 +2216,9 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2182,6 +2274,9 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2239,6 +2334,9 @@
       <c r="O32" t="n">
         <v>0.25</v>
       </c>
+      <c r="P32" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2296,6 +2394,9 @@
       <c r="O33" t="n">
         <v>0.25</v>
       </c>
+      <c r="P33" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2353,6 +2454,9 @@
       <c r="O34" t="n">
         <v>0.25</v>
       </c>
+      <c r="P34" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2410,6 +2514,9 @@
       <c r="O35" t="n">
         <v>0.25</v>
       </c>
+      <c r="P35" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2467,6 +2574,9 @@
       <c r="O36" t="n">
         <v>0.25</v>
       </c>
+      <c r="P36" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2498,242 +2608,254 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
+What</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.5), (' Canada', 1.0), ('.\n', 1.0), ('What', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>What is the location of Simcoe Composite School?</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fill-in-the-Blank</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>Simcoe Composite School is located in Simcoe, Ontario.
 What is the</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I38" t="n">
         <v>0.5</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J38" t="n">
         <v>0.9548416137695312</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K38" t="n">
         <v>0.3465735912322998</v>
       </c>
-      <c r="L37" t="b">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
-      <c r="N37" t="n">
+      <c r="N38" t="n">
         <v>0.5</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O38" t="n">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-8B</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>What is the location of Simcoe Composite School?</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="P38" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>What is the location of Simcoe Composite School?</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>Fill-in-the-Blank</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>15</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="D39" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Simcoe Composite School is located in Simcoe, Ontario.
+What is the</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>What is the location of Simcoe Composite School?</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fill-in-the-Blank</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
 What</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="I40" t="n">
         <v>0.5</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J40" t="n">
         <v>0.9548416137695312</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K40" t="n">
         <v>0.3465735912322998</v>
       </c>
-      <c r="L38" t="b">
-        <v>1</v>
-      </c>
-      <c r="M38" t="inlineStr">
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.5), (' Canada', 1.0), ('.\n', 1.0), ('What', 1.0)]</t>
         </is>
       </c>
-      <c r="N38" t="n">
+      <c r="N40" t="n">
         <v>0.5</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O40" t="n">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-8B</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>What is the location of Simcoe Composite School?</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="P40" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>What is the location of Simcoe Composite School?</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Fill-in-the-Blank</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>15</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="D41" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Simcoe Composite School is located in Simcoe, Ontario.
 What is the</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="L39" t="b">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-8B</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>What is the location of Simcoe Composite School?</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Fill-in-the-Blank</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>15</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>4</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada.
-What</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="L40" t="b">
-        <v>1</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.5), (' Canada', 1.0), ('.\n', 1.0), ('What', 1.0)]</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-8B</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>What is the location of Simcoe Composite School?</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Fill-in-the-Blank</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>15</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>5</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Simcoe Composite School is located in Simcoe, Ontario.
-What is the</t>
-        </is>
-      </c>
       <c r="I41" t="n">
         <v>0.5</v>
       </c>
@@ -2757,6 +2879,9 @@
       <c r="O41" t="n">
         <v>0.4</v>
       </c>
+      <c r="P41" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2815,6 +2940,9 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
+      <c r="P42" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2873,6 +3001,9 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
+      <c r="P43" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2931,6 +3062,9 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
+      <c r="P44" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2989,6 +3123,9 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
+      <c r="P45" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3047,6 +3184,9 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
+      <c r="P46" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3078,8 +3218,8 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-Question: What is the name of the</t>
+          <t>Owen Sound
+Question: What is the name of the school</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3096,13 +3236,16 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('\xa0', 1.0), ('Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+          <t>[(' ', 1.0), ('\xa0', 1.0), ('O', 0.5), ('wen', 1.0), (' Sound', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' school', 1.0)]</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
         <v>-0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3134,8 +3277,8 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-Question: What is the name of the</t>
+          <t>Owen Sound
+Question: What is the name of the school</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3152,13 +3295,16 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('\xa0', 1.0), ('Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+          <t>[(' ', 1.0), ('\xa0', 1.0), ('O', 0.5), ('wen', 1.0), (' Sound', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' school', 1.0)]</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
         <v>-0</v>
       </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3190,8 +3336,8 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Owen Sound
-Question: What is the name of the school</t>
+          <t>Simcoe, Ontario
+Question: What is the name of the</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3208,13 +3354,16 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('\xa0', 1.0), ('O', 0.5), ('wen', 1.0), (' Sound', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' school', 1.0)]</t>
+          <t>[(' ', 1.0), ('\xa0', 1.0), ('Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
         <v>-0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3271,6 +3420,9 @@
       <c r="O50" t="n">
         <v>-0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3302,8 +3454,8 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Simcoe, Ontario
-Question: What is the name of the</t>
+          <t>Owen Sound
+Question: What is the name of the school</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3320,13 +3472,16 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('\xa0', 1.0), ('Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+          <t>[(' ', 1.0), ('\xa0', 1.0), ('O', 0.5), ('wen', 1.0), (' Sound', 1.0), ('\n', 1.0), ('Question', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' school', 1.0)]</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>-0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3384,6 +3539,9 @@
       <c r="O52" t="n">
         <v>0.3666666666666667</v>
       </c>
+      <c r="P52" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3442,6 +3600,9 @@
       <c r="O53" t="n">
         <v>0.3666666666666667</v>
       </c>
+      <c r="P53" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3499,6 +3660,9 @@
       <c r="O54" t="n">
         <v>0.3666666666666667</v>
       </c>
+      <c r="P54" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3557,6 +3721,9 @@
       <c r="O55" t="n">
         <v>0.3666666666666667</v>
       </c>
+      <c r="P55" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3615,6 +3782,9 @@
       <c r="O56" t="n">
         <v>0.3666666666666667</v>
       </c>
+      <c r="P56" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3671,6 +3841,9 @@
       <c r="O57" t="n">
         <v>1</v>
       </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3727,6 +3900,9 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3783,6 +3959,9 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3839,6 +4018,9 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3895,6 +4077,9 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3953,6 +4138,9 @@
       <c r="O62" t="n">
         <v>0.25</v>
       </c>
+      <c r="P62" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4011,6 +4199,9 @@
       <c r="O63" t="n">
         <v>0.25</v>
       </c>
+      <c r="P63" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4068,6 +4259,9 @@
       <c r="O64" t="n">
         <v>0.25</v>
       </c>
+      <c r="P64" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4126,6 +4320,9 @@
       <c r="O65" t="n">
         <v>0.25</v>
       </c>
+      <c r="P65" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4183,6 +4380,9 @@
       <c r="O66" t="n">
         <v>0.25</v>
       </c>
+      <c r="P66" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4214,8 +4414,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>) (1 point) Simcoe, Ontario
-What is the location of Sim</t>
+          <t>) (1 point) 1. Simcoe 2. Port Dover</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4232,13 +4431,16 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0)]</t>
+          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' ', 0.5), ('1', 1.0), ('.', 1.0), (' Sim', 1.0), ('coe', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' Port', 1.0), (' Dover', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
         <v>-0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4270,8 +4472,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>) (1 point) Simcoe, Ontario
-What is the location of Sim</t>
+          <t>) (1 point) 1. Simcoe 2. Port Dover</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4288,13 +4489,16 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0)]</t>
+          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' ', 0.5), ('1', 1.0), ('.', 1.0), (' Sim', 1.0), ('coe', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' Port', 1.0), (' Dover', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>-0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4326,7 +4530,8 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>) (1 point) 1. Simcoe 2. Port Dover</t>
+          <t>) (1 point) Simcoe, Ontario
+What is the location of Sim</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4343,13 +4548,16 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' ', 0.5), ('1', 1.0), ('.', 1.0), (' Sim', 1.0), ('coe', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' Port', 1.0), (' Dover', 1.0), (' ', 1.0)]</t>
+          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0)]</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
         <v>-0</v>
       </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4381,30 +4589,33 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>) Simcoe Composite School is located in Simcoe, Ontario. The school is</t>
+          <t>) Simcoe Composite School is located in Simcoe, Ontario. Simcoe is</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.11275265365839</v>
+        <v>0.03230417519807816</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8645864725112915</v>
+        <v>0.7954579591751099</v>
       </c>
       <c r="K70" t="n">
-        <v>0.8095403909683228</v>
+        <v>0.9481958150863647</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>[(' Sim', 0.2227), ('coe', 1.0), (' Composite', 0.6514), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' The', 0.7773), (' school', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sim', 0.2227), ('coe', 1.0), (' Composite', 0.6514), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' Sim', 0.2227), ('coe', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
         <v>-0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4436,8 +4647,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>) (1 point) Simcoe, Ontario
-What is the location of Sim</t>
+          <t>) (1 point) 1. Simcoe 2. Port Dover</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4454,13 +4664,16 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' Sim', 1.0)]</t>
+          <t>[(' (', 0.7773), ('1', 1.0), (' point', 1.0), (')', 1.0), (' ', 0.5), ('1', 1.0), ('.', 1.0), (' Sim', 1.0), ('coe', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' Port', 1.0), (' Dover', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
         <v>-0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4518,6 +4731,9 @@
       </c>
       <c r="O72" t="n">
         <v>0.8875</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="73">
@@ -4578,6 +4794,9 @@
       <c r="O73" t="n">
         <v>0.8875</v>
       </c>
+      <c r="P73" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4636,6 +4855,9 @@
       <c r="O74" t="n">
         <v>0.8875</v>
       </c>
+      <c r="P74" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4694,6 +4916,9 @@
       <c r="O75" t="n">
         <v>0.8875</v>
       </c>
+      <c r="P75" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4752,6 +4977,9 @@
       <c r="O76" t="n">
         <v>0.8875</v>
       </c>
+      <c r="P76" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4808,7 +5036,10 @@
         <v>0.5</v>
       </c>
       <c r="O77" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="78">
@@ -4841,184 +5072,193 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
+          <t>1 Simcoe Street, Simcoe, Ontario
+QSTN:</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>What is the location of Simcoe Composite School?</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Question-Answer Pairs</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>15</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F79" t="b">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1 Simcoe Street, Simcoe, Ontario
+QSTN:</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>What is the location of Simcoe Composite School?</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Question-Answer Pairs</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>15</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F80" t="b">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1 Simcoe Street, Simcoe, Ontario
+QSTN:</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.9548416137695312</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.3465735912322998</v>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0)]</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>What is the location of Simcoe Composite School?</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Question-Answer Pairs</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>15</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F81" t="b">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>Simcoe, Ontario
 QSTN: What is the capital of Canada</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="L78" t="b">
-        <v>1</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>[(' Sim', 0.5), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' Canada', 1.0)]</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-8B</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>What is the location of Simcoe Composite School?</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Question-Answer Pairs</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>15</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F79" t="b">
-        <v>0</v>
-      </c>
-      <c r="G79" t="n">
-        <v>3</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>1 Simcoe Street, Simcoe, Ontario
-QSTN:</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="L79" t="b">
-        <v>0</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0)]</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-8B</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>What is the location of Simcoe Composite School?</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Question-Answer Pairs</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>15</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F80" t="b">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>4</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>1 Simcoe Street, Simcoe, Ontario
-QSTN:</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="L80" t="b">
-        <v>0</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>[(' ', 0.5), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('\n', 1.0), ('Q', 1.0), ('ST', 1.0), ('N', 1.0), (':', 1.0)]</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-8B</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>What is the location of Simcoe Composite School?</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Question-Answer Pairs</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>15</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F81" t="b">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>5</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Simcoe, Ontario
-QSTN: What is the capital of Canada</t>
-        </is>
-      </c>
       <c r="I81" t="n">
         <v>0.5</v>
       </c>
@@ -5040,7 +5280,10 @@
         <v>0.5</v>
       </c>
       <c r="O81" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="82">
@@ -5099,6 +5342,9 @@
       <c r="O82" t="n">
         <v>0.5</v>
       </c>
+      <c r="P82" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5156,6 +5402,9 @@
       <c r="O83" t="n">
         <v>0.5</v>
       </c>
+      <c r="P83" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5213,6 +5462,9 @@
       <c r="O84" t="n">
         <v>0.5</v>
       </c>
+      <c r="P84" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5270,6 +5522,9 @@
       <c r="O85" t="n">
         <v>0.5</v>
       </c>
+      <c r="P85" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5327,6 +5582,9 @@
       <c r="O86" t="n">
         <v>0.5</v>
       </c>
+      <c r="P86" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5358,30 +5616,33 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
+          <t>Simcoe Composite School is located at 1 Maple Avenue, Simcoe,</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.2227001488208771</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9047210812568665</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.334479808807373</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Maple', 0.2227), (' Avenue', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="n">
         <v>-0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5413,30 +5674,33 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
+          <t>Simcoe Composite School is located at 1 Maple Avenue, Simcoe,</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.2227001488208771</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9047210812568665</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.334479808807373</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Maple', 0.2227), (' Avenue', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
         <v>-0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5492,6 +5756,9 @@
       <c r="O89" t="n">
         <v>-0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5547,6 +5814,9 @@
       <c r="O90" t="n">
         <v>-0</v>
       </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5602,6 +5872,9 @@
       <c r="O91" t="n">
         <v>-0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5660,6 +5933,9 @@
       <c r="O92" t="n">
         <v>0.7</v>
       </c>
+      <c r="P92" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5718,6 +5994,9 @@
       <c r="O93" t="n">
         <v>0.7</v>
       </c>
+      <c r="P93" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5775,6 +6054,9 @@
       <c r="O94" t="n">
         <v>0.7</v>
       </c>
+      <c r="P94" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5832,6 +6114,9 @@
       <c r="O95" t="n">
         <v>0.7</v>
       </c>
+      <c r="P95" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5888,6 +6173,9 @@
       </c>
       <c r="O96" t="n">
         <v>0.7</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="97">
@@ -5944,6 +6232,9 @@
       <c r="O97" t="n">
         <v>-0</v>
       </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5975,30 +6266,33 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Simcoe Composite School is located at 1 Simcoe Street, Simcoe</t>
+          <t>Simcoe Composite School is located at 1000 Simcoe Street, Sim</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.3256774246692657</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9279384613037109</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="K98" t="n">
-        <v>0.6258097887039185</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 0.5), (' Sim', 0.6514), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('100', 0.5), ('0', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0)]</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="n">
         <v>-0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6054,6 +6348,9 @@
       <c r="O99" t="n">
         <v>-0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6109,6 +6406,9 @@
       <c r="O100" t="n">
         <v>-0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6163,6 +6463,9 @@
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
         <v>-0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
